--- a/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_cfd_011/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_cfd_011/extracted.xlsx
@@ -279,6 +279,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -429,6 +434,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="G4" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -500,11 +510,6 @@
       </text>
     </comment>
     <comment ref="F6" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="G6" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1296,12 +1301,12 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Predict compressor-face pressure recovery and distortion for the XU-43 1.2 m S-duct inlet at three throttle points to support bleed-slot sizing and operability screening</t>
+          <t>Predict compressor-face pressure recovery and distortion for XU-43 S-duct inlet to support bleed-slot sizing and operability screening</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>Steady and unsteady RANS CFD (Ansys Fluent 2023R1) of a 1.2 m diameter S-duct inlet at sea-level static conditions (M≈0.25, ReD≈5.1e6). Quantities of interest are area-averaged total-pressure recovery and DC60 distortion index at the compressor-face rake plane R1. Results are used for concept trade selection and bleed-schedule screening prior to A-test taxi runs; explicitly not intended to set surge red-lines or support initial flight clearance beyond advisory use.</t>
+          <t>Steady and unsteady RANS CFD of a 1.2 m diameter S-duct inlet at M≈0.25, ReD≈5.1e6, sea-level static conditions. The model provides distortion maps (DC60, swirl intensity) and area-averaged total pressure recovery at three throttle points (85/100/115% design mass flow) to screen two bleed schedules and two anti-ice lip geometries ahead of A-test taxi runs. Results are advisory only and are not intended to certify surge margins.</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
@@ -1335,9 +1340,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>report.md</t>
         </is>
       </c>
       <c r="L3" s="12" t="inlineStr">
@@ -1456,7 +1461,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Advisory distortion and recovery accuracy for bleed-slot sizing</t>
+          <t>Advisory distortion and recovery accuracy for operability screening</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1466,7 +1471,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>CFD predictions of DC60 and total-pressure recovery must be sufficiently accurate to distinguish between bleed schedules and lip geometries for concept trade selection and operability screening; not used to certify surge margins. Accepted uncertainty bands are ±0.8% absolute on DC60 and ±0.6% on recovery for discriminating between variants.</t>
+          <t>CFD predictions of DC60 and total pressure recovery must be sufficiently accurate (within ±0.8% absolute DC60, ±0.6% recovery) to support concept trade selection and bleed-slot sizing without certifying surge margins or flight red-lines.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -1488,12 +1493,12 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>Ansys Fluent 2023R1 RANS/IDDES S-duct CFD model</t>
+          <t>Ansys Fluent 2023R1 RANS/IDDES S-duct model</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Poly-hexcore RANS (k-ω SST baseline) and one IDDES model of the XU-43 S-duct; three mesh levels (12M/24M/48M cells); steady and unsteady operating points at 85/100/115% design mass flow.</t>
+          <t>Poly-hexcore CFD model of the XU-43 S-duct (12M/24M/48M cells) using k-ω SST baseline; SA-neg and IDDES variants for off-design; steady RANS primary with one URANS/IDDES transient case.</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1515,7 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>36-port Kiel rake, 16 static taps, and 5-hole probe measurements at rake plane R1; ReD=4.7e6, M=0.23; inlet TI 4.5–5.2%; used as primary validation comparator for recovery and DC60.</t>
+          <t>36-port Kiel rake, 16 static taps, and 5-hole probe measurements at ReD≈4.7e6, M≈0.23; provides recovery, DC60, and swirl intensity for comparison against CFD predictions.</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1527,12 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>XD-17 prior S-duct correlation data</t>
+          <t>XD-17 S-duct prior correlation data</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Internal read-across from previous XD-17 S-duct program at M=0.3; recovery error within 1% and DC60 within 0.5% at three flow points, though a separate memo notes 2–3% recovery bias and 5–7% DC60 under-prediction due to geometry smoothing.</t>
+          <t>Internal read-across data from previous XD-17 S-duct program at M=0.3; recovery error within 1% and DC60 within 0.5% in three-point comparison, with noted geometry-smoothing caveat.</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1984,12 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Three-level mesh refinement (12M, 24M, 48M cells) with steady RANS k-ω SST at 100% design mass flow. Recovery values: 0.982/0.986/0.985; DC60 values: 6.8%/6.5%/6.6% showing non-monotonic behavior.</t>
+          <t>Three-level mesh refinement (12M, 24M, 48M cells) for steady RANS at 100% flow; GCI on recovery reported and recomputed; DC60 shows non-monotonic trend.</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>Self-convergence across mesh levels; GCI analysis</t>
+          <t>Richardson extrapolation / GCI; no external reference</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
@@ -1994,12 +1999,12 @@
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
-          <t>Grid Convergence Index (GCI); Richardson extrapolation with observed order 1.9</t>
+          <t>Grid Convergence Index (GCI); observed order ≈1.9</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>GCI on recovery reported as 0.8%; recalculated as ~1.7%. DC60 envelope ±0.4% absolute (non-monotonic).</t>
+          <t>GCI recovery ≈1.7% (recomputed); DC60 envelope ±0.4% absolute (non-monotonic)</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr">
@@ -2011,7 +2016,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Solver convergence monitoring</t>
+          <t>CFD vs. AeroLab West rig — 100% flow baseline</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
@@ -2021,22 +2026,27 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Residual and integral monitor convergence for steady RANS baseline cases. Continuity and turbulence residuals reduced &gt;3 orders; momentum &gt;4 orders. Mass imbalance &lt;0.1%; recovery change &lt;0.05% over 2000 iterations. URANS/IDDES time-step independence claimed for three Δt levels but logbook confirms only two levels executed.</t>
+          <t>Comparison of area-averaged recovery, DC60, and swirl intensity between CFD (24M SST) and rig measurements at matched geometry, 100% mass flow, bleed off.</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>Internal convergence targets</t>
+          <t>AeroLab West Kiel rake and 5-hole probe data</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>Inlet TI sensitivity and turbulence model spread quoted as uncertainty components</t>
         </is>
       </c>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>Mass imbalance &lt;0.1%; recovery variation &lt;0.05% at plateau</t>
+          <t>Recovery Δ=+0.7% (CFD 0.986 vs test 0.979); DC60 Δ=−0.6% abs (CFD 6.5% vs test 7.1%); swirl Δ=−0.8° (CFD 3.2° vs test 4.0°)</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
@@ -2048,7 +2058,7 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Rig comparison — recovery and DC60 at 100% flow</t>
+          <t>Turbulence model sensitivity — SST vs SA-neg vs IDDES</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
@@ -2058,12 +2068,12 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Comparison of CFD predictions (24M baseline mesh, k-ω SST, TI=1%) against AeroLab West rig measurements at 100% design mass flow with baseline lip and bleed off. Recovery: CFD 0.986 vs. test 0.979 (Δ=+0.7%); DC60: CFD 6.5% vs. test 7.1% (Δ=–0.6% absolute). Swirl intensity: CFD 3.2° vs. test 4.0°. Noted discrepancy: alternate draft V&amp;V sheet lists test recovery as 0.982. Inlet TI mismatch: CFD used 1% vs. measured rig TI of 4.5–5.2%. Re mismatch at 85% flow closer to 8%.</t>
+          <t>Comparison of recovery and DC60 predictions across three turbulence closures at 85% and 100% flow to quantify model-form uncertainty.</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>AeroLab West Subsonic Inlet Rig experimental data</t>
+          <t>Internal cross-model comparison; IDDES treated as higher-fidelity reference</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
@@ -2073,12 +2083,12 @@
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
-          <t>Sensitivity study — inlet TI variation 1→5%: recovery –0.3%, DC60 +0.5%; turbulence model spread SST vs SA-neg vs IDDES quoted as model-form uncertainty</t>
+          <t>Model-form spread used as bias estimate</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>Recovery error +0.7% (or +0.4% depending on test reference); DC60 error –0.6% absolute; swirl intensity error –0.8°</t>
+          <t>SST vs SA-neg at 85%: Δrecovery=−0.4%, ΔDC60=+0.7%; IDDES at 100%: recovery 0.983, DC60 7.0% vs SST 0.986/6.5%</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
@@ -2090,7 +2100,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>Turbulence model sensitivity study</t>
+          <t>Solver residual and iterative convergence check</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -2100,27 +2110,22 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Comparison of k-ω SST, SA-neg, and IDDES (12M coarse grid) predictions at 85% and 100% flow. SST vs SA-neg at 85% flow: Δrecovery=–0.4%, ΔDC60=+0.7%. IDDES at 100% flow: recovery 0.983, DC60 7.0% with ±1.5% DC60 swing over 0.1 s windows. γ–Reθ transition model probed on two runs with no conclusive change.</t>
+          <t>Monitoring of continuity, momentum, and turbulence residuals plus integral mass imbalance and recovery stabilization over final 2000 iterations for steady RANS cases.</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>Cross-model comparison; partial comparison to rig DC60 of 7.1%</t>
+          <t>Internal convergence targets</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G6" s="13" t="inlineStr">
-        <is>
-          <t>Model-form spread treated as bias uncertainty (~0.7% DC60, 0.4% recovery)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>Turbulence model spread: 0.4% recovery, 0.7% DC60</t>
+          <t>Continuity/turbulence residuals &gt;3 orders; momentum &gt;4 orders; mass imbalance &lt;0.1%; recovery change &lt;0.05% over 2k iterations</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
@@ -2132,7 +2137,7 @@
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>XD-17 prior program read-across</t>
+          <t>XD-17 prior program read-across correlation</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
@@ -2142,12 +2147,12 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Prior S-duct (XD-17, M=0.3) showed recovery error within 1% and DC60 within 0.5% across three flow points. Separate memo notes conflicting result: 2–3% recovery bias and 5–7% DC60 under-prediction due to excessive geometry smoothing of inner-bend scallop.</t>
+          <t>Read-across from previous XD-17 S-duct CFD-to-test correlation at M=0.3 to provide historical credibility context for the current model approach.</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>XD-17 experimental data</t>
+          <t>XD-17 rig test data</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
@@ -2157,7 +2162,7 @@
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>Recovery error 1% (best case) to 2–3% (smoothed geometry); DC60 error 0.5% to 5–7%</t>
+          <t>Recovery error within 1%, DC60 within 0.5% (clean geometry); 2–3% recovery bias and 5–7% DC60 under-prediction noted for smoothed geometry variant</t>
         </is>
       </c>
       <c r="I7" s="13" t="inlineStr">
@@ -2311,12 +2316,12 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Primary solver version controlled and commercially verified; meshing and post-processing tools identified; workflow under version control.</t>
+          <t>Commercial solver with documented version control and traceability for primary cases</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Primary solver is Ansys Fluent 2023R1 (commercial, implying vendor QA); meshing in Pointwise 18.5; post-processing in Tecplot 360 EX 2022 R2. Case templates and journals stored in GitLab repo sduct-cfdbeta tag v0.7; meshes on PFS with md5 checksums. Two early scoping runs in OpenFOAM v10 on a local workstation are noted as not bitwise comparable. Anti-ice lip sweep generated outside the repo by an intern script with no tag — a gap. Solver version freeze to v0.8 is committed but not yet executed at time of report.</t>
+          <t>Primary solver Ansys Fluent 2023R1 is a commercial code with implied vendor QA. Case templates and journals stored in GitLab repo sduct-cfdbeta at tag v0.7 with md5 checksums on meshes. Pointwise 18.5 and Tecplot 360 EX 2022 R2 also commercial tools. Gaps: two early scoping runs in OpenFOAM on a local workstation outside repo; anti-ice lip sweep generated by an intern script with no repo tag, settings only in slide notes. Solver version freeze (v0.8 tag) committed but not yet executed at time of report.</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -2345,12 +2350,12 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Solver has been demonstrated to reproduce known benchmark solutions or analytical references for internal duct flows.</t>
+          <t>Solver verified against known benchmark cases or analytical solutions for relevant flow regime</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>No explicit benchmark comparisons (analytical solutions, MMS, or standard benchmark problems) are documented in this report. Commercial solver status implies vendor-level code verification, and prior XD-17 program provides some indirect evidence of code behavior. No dedicated code verification activity is reported for this study.</t>
+          <t>No explicit benchmark or manufactured-solution verification is described for this study. Fluent 2023R1 as a commercial code carries implicit vendor verification. Prior XD-17 correlation provides some indirect code credibility, but no dedicated numerical verification against analytical solutions or standard S-duct benchmarks is documented in the evidence corpus.</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -2379,12 +2384,12 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>Monotonic mesh convergence demonstrated; GCI or equivalent uncertainty estimate reported consistently for all QoIs.</t>
+          <t>Monotonic mesh convergence with GCI &lt; 1% on primary QoIs</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Three mesh levels (12M/24M/48M) were run with steady RANS k-ω SST. Recovery shows near-convergence (0.982/0.986/0.985) but the non-monotonic DC60 trend (6.8/6.5/6.6%) prevents formal Richardson extrapolation. GCI on recovery reported as 0.8% but recalculated as ~1.7% with observed order 1.9 — internal inconsistency unresolved. Anti-ice lip sweeps and two parametric studies used a cost-reduced 9.6M wall-function mesh inconsistent with the baseline, introducing additional unquantified discretization uncertainty. IDDES used a coarse 12M grid. The "grid-independent at &lt;0.5%" claim is not supported by the recalculation.</t>
+          <t>Three-level mesh refinement study performed (12M/24M/48M cells). GCI on recovery reported as 0.8% but recomputed as ≈1.7% using observed order 1.9. DC60 shows non-monotonic trend across mesh levels, invalidating standard GCI application; envelope value of ±0.4% absolute is used instead. Two anti-ice lip variant sweeps conducted on a cost-reduced 9.6M wall-function mesh inconsistent with the baseline, introducing unquantified additional discretization error for those cases. Time-step independence claimed for IDDES but only two Δt levels actually executed versus the stated three.</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -2406,19 +2411,19 @@
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="14" t="n">
         <v>3</v>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Residuals reduced by sufficient orders of magnitude; key integral monitors plateau; mass imbalance within acceptable tolerance.</t>
+          <t>Residuals reduced by at least 3 orders of magnitude; key integral quantities stabilized</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>Continuity and turbulence residuals reduced &gt;3 orders; momentum &gt;4 orders on baseline cases. Mass imbalance &lt;0.1%; recovery variation &lt;0.05% over last 2000 iterations. Time-step independence for the URANS/IDDES case is incomplete — only two of three claimed Δt levels were executed, and early memo claiming full verification is contradicted by the logbook.</t>
+          <t>Continuity and turbulence residuals reduced &gt;3 orders of magnitude; momentum &gt;4 orders on baseline cases. Mass imbalance &lt;0.1% and recovery change &lt;0.05% over final 2000 iterations confirm integral stability. Pseudo-transient CFL ramping (5→100) documented. IDDES case used Δt=1e-4 s with 10 sub-iterations over 0.3 s physical time. Minor gap: time-step independence for IDDES not fully verified (two levels only).</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -2447,12 +2452,12 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Model setup independently reviewed; boundary conditions verified against requirements; mesh quality checked; all runs traceable to controlled configuration.</t>
+          <t>Independent review of boundary conditions, mesh setup, and post-processing for all production cases</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Paired analyst reviews conducted weekly (lead 8 yr experience, second analyst 2 yr). GitLab version control for main cases. However, several use-error risks are documented: 180° periodic sector used despite stated full 360° geometry; anti-ice lip sweep run outside repo by intern without tag; TI set to 1% for most runs while rig data indicates 4.5–5.2%; bleed ring modeled as ideal despite measured discharge coefficient of 0.86±0.04; m=2 swirl content in rig not reproduced in CFD. Wall-treatment inconsistency (y+≈1 baseline vs. y+≈40–60 for lip sweeps) not flagged until slide review.</t>
+          <t>Paired analyst reviews conducted each Friday (lead with 8 years experience, second analyst 2 years). GitLab repo provides some configuration control for primary cases. However, the anti-ice lip sweep was set up outside the repo by an intern with settings only in slide notes — no formal independent review documented for those cases. The 180°/360° periodic sector inconsistency (kickoff stated full 360°, straight-through used 180°) was identified but not formally resolved. Inlet TI discrepancy between CFD (1%) and rig data (4.5–5.2%) for most production cases represents an uncorrected setup error. Bleed ring modeled as ideal despite measured discharge coefficient of 0.86±0.04.</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -2481,12 +2486,12 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Turbulence closure selection justified; known limitations documented; model form uncertainty estimated.</t>
+          <t>Turbulence model selection justified with documented limitations; governing physics assumptions stated</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>k-ω SST with production limiter is the baseline; rationale is by convention for adverse-pressure-gradient internal flows. SA-neg and IDDES explored for off-design. Fully turbulent assumption adopted; transition modeled only in two sensitivity runs with no conclusive outcome. Model-form spread (SST vs SA-neg vs IDDES) used as a proxy for model-form uncertainty (~0.7% DC60, 0.4% recovery). IDDES showed intermittent reattachment and ±1.5% DC60 swing — recognized limitation. Known gaps: surface roughness, insect accretion, and bleed discharge coefficient idealization documented but not resolved. Conflicting total uncertainty figures (1.1% vs. 3.5% recovery) indicate convention not yet settled.</t>
+          <t>k-ω SST with production limiter selected as baseline for adverse pressure gradient S-duct flow — appropriate and stated. SA-neg and IDDES sensitivity variants executed, showing ≈0.7% DC60 and 0.4% recovery spread. Fully turbulent assumption documented; transition only probed with γ-Reθ in two trial runs with no conclusive change. IDDES on coarse 12M mesh showed ±1.5% DC60 swing over 0.1 s windows, indicating unsteady content that steady RANS cannot capture. Surface roughness, insect accretion, and transition not modeled — limitations acknowledged. Model-form uncertainty quantified as spread across closures and included in total uncertainty budget.</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -2515,12 +2520,12 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Boundary conditions derived from measurements or well-justified assumptions; input uncertainty characterized; geometry accurately represents hardware including key features.</t>
+          <t>Inlet boundary conditions and geometry inputs characterized with stated uncertainties; bleed and anti-ice geometry accurately represented</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Geometry from CAD including diverter, bleed ring, and two lip variants; fasteners, paint steps, and sub-1 mm fillets suppressed — likely minor. Inlet total pressure and temperature specified from standard conditions; mass flow targets set to hardware operating points. Turbulence intensity set at 1% (fan honeycomb assumption) contradicting rig measurement of 4.5–5.2% — a significant input mismatch for most runs. Bleed ring discharge coefficient measured at 0.86±0.04 in bench test but modeled as ideal in CFD — deferred. Swirl profile imposed as m=1 mode only; rig produced additional m=2 content. Two "rig-match" runs at TI=5% executed but not the primary basis. Input uncertainty characterized only via one-at-a-time sensitivities; the planned Latin hypercube was replaced by a limited fractional factorial (k=3, N=8 equivalent) with a non-robust kriging surrogate on five points.</t>
+          <t>CAD geometry includes bleed ring and anti-ice lip variants with minor features suppressed (fasteners, paint step, gaps &lt;0.8 mm, fillets &lt;1 mm) — omissions documented. Inlet total pressure (101.3 kPa) and temperature (300 K) from standard conditions. Inlet TI set to 1% for most cases based on assumed honeycomb effectiveness, inconsistent with measured rig TI of 4.5–5.2%; only two rig-match runs at 5% executed. Swirl profile (6° peak, m=1) imposed but rig produced m=2 content not modeled — impact stated as TBD. Bleed ring discharge coefficient measured at 0.86±0.04 but modeled as ideal. Sensitivity to TI and bleed fraction quantified one-at-a-time. DOE (fractional factorial k=3, 2-level) executed but kriging surrogate based on only 7 points deemed not robust.</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -2549,12 +2554,12 @@
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Test article is geometry-representative; number of test configurations adequate for primary validation comparator.</t>
+          <t>Test article geometry representative of CFD model; adequate instrumentation coverage</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>AeroLab West rig uses matched geometry with removable bleed ring, 36-port Kiel rake at R1, 16 static taps, and 5-hole probe. One primary geometry configuration tested (baseline lip, bleed off) at 100% flow provides the main validation point. Number of test configurations and replicates not stated. Re-mismatch between rig (4.7e6) and CFD design intent (5.1e6) is noted; at 85% flow the mismatch increases to ~8%. Test article adequacy for the anti-ice lip variants and bleed-on cases not demonstrated — rig data for those conditions not referenced.</t>
+          <t>Single matched-geometry test article used in AeroLab West rig with removable bleed ring. 36-port Kiel rake at R1 and 16 static taps provide reasonable spatial coverage of the compressor face; 5-hole probe used for swirl. No multiple specimens or statistical characterization of manufacturing variability. One test configuration reported at 100% flow for baseline validation — limited operating-point coverage for the three-throttle-point COU. No documentation of sample size justification.</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -2583,12 +2588,12 @@
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Test conditions measured with calibrated instruments; measurement uncertainty reported; inlet conditions (TI, Re, M) controlled and documented.</t>
+          <t>Test Reynolds number and Mach number matched to CFD within stated tolerances; calibrated instrumentation with documented measurement uncertainty</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Facility log reports ReD=4.7e6 (±3%) and M=0.23; inlet TI measured by hot-wire as 4.5–5.2%. Kiel rake and static taps used at R1; 5-hole probe for swirl. Measurement uncertainty on recovery and DC60 not explicitly quantified in the report. Inconsistency in test recovery reference (0.979 vs. 0.982) unresolved — different rake calibration assumptions suspected. Re mismatch at 85% flow (~8%) not adequately controlled. No ASTM/ISO standard referenced for rake calibration or data reduction.</t>
+          <t>Facility log states ReD=4.7e6 (±3%), M=0.23; inlet TI measured by hot-wire at 4.5–5.2%. Kiel rake and static taps imply calibrated instrumentation. However, Re mismatch between CFD (5.1e6) and rig (4.7e6) is approximately 8% at 85% flow (not the claimed 2%). Swirl generator produced m=2 harmonic content not controlled against CFD inputs. Conflicting test recovery values (0.979 vs 0.982) between facility log and draft V&amp;V sheet indicate data traceability issue. Rake calibration assumption not confirmed as consistent across both references.</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -2617,12 +2622,12 @@
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>CFD boundary conditions matched to measured test conditions; deviations documented and sensitivity-assessed.</t>
+          <t>CFD boundary conditions demonstrably match test conditions including TI, Re, and swirl content</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>For the primary validation point (100% flow, baseline lip, bleed off): Re matched within stated 2% but actual mismatch is ~8% at 85% flow; M nominally matched (0.25 CFD vs. 0.23 rig). Inlet TI set to 1% in most CFD runs vs. rig 4.5–5.2% — a documented and partially addressed mismatch (two rig-match runs at 5% conducted). Swirl m=2 content in rig not reproduced in CFD; impact TBD. Two "rig-match" sensitivity runs at TI=5% provide partial equivalency evidence. Bleed ring modeled as ideal vs. measured Cd=0.86±0.04. Propagation of these input mismatches to output uncertainty is only partially quantified via one-at-a-time sensitivities.</t>
+          <t>Most production CFD cases set TI=1% while rig measured 4.5–5.2% — a substantial mismatch addressed in only two rig-match runs. Re mismatch up to 8% at 85% flow. Swirl m=2 content in rig not replicated in CFD. Geometry periodic-sector assumption (180° vs 360°) not reconciled against full-annulus rig. Two rig-match runs at TI=5% represent partial alignment. Bleed-off condition provides one aligned operating point, but mismatch in TI and swirl mode content limits equivalency confidence.</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -2651,12 +2656,12 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Quantitative comparison of CFD predictions to test data for primary QoIs (recovery, DC60) with uncertainty bands; multiple operating points compared.</t>
+          <t>Quantitative comparison of recovery, DC60, and swirl intensity with uncertainty bounds at multiple operating points</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Recovery: CFD 0.986 vs. test 0.979 (Δ=+0.7%), though test reference is uncertain (0.979 vs. 0.982). DC60: CFD 6.5% vs. test 7.1% (Δ=–0.6% absolute). Swirl intensity: CFD 3.2° vs. test 4.0°. Comparison conducted at one operating point (100% flow, baseline configuration). No comparison reported at 85% or 115% flow points. No comparison for bleed-on or lip-variant configurations against test data. Uncertainty bands on the comparison are not formally computed as a validation metric — numerical uncertainty (±1.7% recovery, ±0.4% DC60) and input BC uncertainty (±0.5% DC60) are quoted separately but not combined into a formal validation uncertainty interval for the comparison. Prior XD-17 program provides additional comparison points but with conflicting conclusions.</t>
+          <t>Quantitative comparison at 100% flow baseline: recovery Δ=+0.7% (CFD 0.986 vs test 0.979, with conflicting test reference 0.982), DC60 Δ=−0.6% absolute, swirl intensity Δ=−0.8°. Total uncertainty budget quoted as 1.1% (numerical+BC RSS) to 3.5% (including model-form expanded) with unresolved convention. Only one operating point (100% flow) directly compared to rig; 85% and 115% throttle points not validated against test data. XD-17 read-across provides supporting correlation but with geometry-smoothing caveat and conflicting bias estimates in the same memo (within 1% vs 2–3% bias).</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -2685,12 +2690,12 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>QoIs (recovery, DC60, swirl intensity) directly address the decision need (bleed-slot sizing, operability screening) and are measurable both computationally and experimentally.</t>
+          <t>DC60, swirl intensity, and area-averaged total pressure recovery are measurable both computationally and experimentally and directly address operability screening needs</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>DC60, area-averaged total-pressure recovery, and swirl intensity at the compressor-face rake plane R1 are standard inlet distortion QoIs directly relevant to compressor operability and bleed-slot sizing. All three are computed by CFD and measured by the rig instrumentation (Kiel rake, static taps, 5-hole probe). The COU explicitly limits the role of these QoIs to concept trade screening and does not extend to surge margin certification — an appropriate scope limitation that preserves relevance of the QoIs within the stated use boundaries.</t>
+          <t>DC60 and total pressure recovery are the standard industry QoIs for compressor-face distortion assessment and are directly measurable by the Kiel rake and static taps in the rig. Swirl intensity measured by 5-hole probe. These QoIs directly address the COU of bleed-slot sizing and operability screening. Rake plane R1 (0.2D upstream of exit) used consistently in both CFD and test. QoIs are not surge margin or flight certification metrics, consistent with the stated advisory use boundary.</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -2719,12 +2724,12 @@
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>Validation conditions (geometry, Re, M, operating points, distortion inputs) sufficiently match the COU envelope; gaps to full COU coverage identified and bounded.</t>
+          <t>Validation covers all three throttle points and both bleed schedules at conditions representative of ground-run operation</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>Rig validation geometry is matched (removable bleed ring, same S-duct). Primary operating condition (100% flow, baseline lip, bleed off) is within COU. However, several gaps reduce relevance: validation covers only one of three throttle points; no rig data for bleed-on or lip-variant conditions; Re mismatch up to 8% at off-design; TI mismatch (1% CFD vs. 4.5–5.2% rig for most runs); m=2 swirl content not reproduced; anti-ice lip sweeps run on inconsistent wall-function mesh not validated against test data. The draft TTO statement that "CFD-based margins acceptable for taxi and high-speed ground run" extends beyond the stated COU without additional validation evidence. Gaps are acknowledged in Slide 12 with a next-steps plan, but are unresolved at time of this assessment.</t>
+          <t>Validation against rig data covers only the 100% flow, bleed-off, baseline-lip condition. The 85% and 115% throttle points that are part of the COU have no direct experimental comparison. Two bleed schedules and two anti-ice lip variants are part of the COU but the anti-ice variants were run only on an inconsistent wall-function mesh not validated against rig data. The rig was operated at slightly lower Re and different swirl content than the COU conditions. Prior XD-17 read-across partially addresses a similar geometry but at different Mach number and with noted geometry-smoothing discrepancy. The draft TTO statement that "CFD-based margins acceptable for taxi and high-speed ground run" has not been reconciled with the advisory-only designation, creating an unresolved scope gap.</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -2909,7 +2914,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>The CFD model demonstrates partial validation for the primary operating point (100% flow, baseline configuration) with recovery error of +0.7% and DC60 error of –0.6% absolute, which are within the stated advisory use bands. However, multiple unresolved issues prevent acceptance at this stage: (1) conflicting test recovery reference values (0.979 vs. 0.982) undermine the validation comparison; (2) inlet TI mismatch (1% CFD vs. 4.5–5.2% rig) for most runs is a significant uncontrolled input error not fully characterized; (3) mesh non-monotonicity for DC60 and an internally inconsistent GCI estimate (0.8% reported vs. 1.7% recalculated) leave discretization uncertainty unresolved; (4) anti-ice lip variant sweeps were conducted on an uncontrolled wall-function mesh generated outside version control, making those results unreliable for decision support; (5) time-step independence for the IDDES case is incomplete; (6) bleed ring discharge coefficient idealization (Cd assumed 1.0 vs. measured 0.86±0.04) is unresolved; (7) validation covers only one of three required throttle points. The model may be re-submitted for acceptance following completion of the September 9 commitments: rig-TI-matched baseline rerun on the 24M y+≈1 mesh, reconciliation of test recovery reference, re-run of lip variants on consistent y+≈1 mesh, and delivery of updated uncertainty bounds covering all three throttle points.</t>
+          <t>The model demonstrates partial but insufficient credibility for the stated COU at this stage. Key deficiencies preclude acceptance: (1) validation against rig data is limited to a single operating point (100% flow, bleed off) of the three-throttle-point COU; (2) the primary inlet TI boundary condition is inconsistent with measured rig conditions for most production cases; (3) anti-ice lip variant results were generated on a coarser, wall-function mesh outside version control, making those trade comparisons unreliable; (4) the conflicting test recovery reference values (0.979 vs 0.982) have not been reconciled; (5) the Re mismatch at 85% flow (~8%) exceeds the claimed 2% tolerance; (6) the draft TTO language permitting CFD-based margins for taxi/ground runs has not been reconciled with the advisory-only designation. Acceptance is contingent on completing the corrective actions committed for the September 9 delivery: aligning inlet TI and swirl content with rig conditions, re-running anti-ice lip variants on y+≈1 mesh under version control, reconciling test reference data, and providing validated predictions at 85% and 115% throttle points before A-test use.</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
